--- a/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2488135_PROCESSED_CHRONO.xlsx
+++ b/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2488135_PROCESSED_CHRONO.xlsx
@@ -553,7 +553,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>M. GEDEAO YIMBU</t>
+          <t>D. MOUHAMED KHALIFA</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -565,73 +565,73 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>6.5919</v>
+        <v>4.3973</v>
       </c>
       <c r="E2" t="n">
-        <v>4.4327</v>
+        <v>5.209</v>
       </c>
       <c r="F2" t="n">
-        <v>2.1592</v>
+        <v>-0.8117</v>
       </c>
       <c r="G2" t="n">
-        <v>3.0631</v>
+        <v>0.4945</v>
       </c>
       <c r="H2" t="n">
-        <v>2.797</v>
+        <v>0.6157</v>
       </c>
       <c r="I2" t="n">
-        <v>0.2661</v>
+        <v>-0.1211</v>
       </c>
       <c r="J2" t="n">
-        <v>3.0209</v>
+        <v>1.6657</v>
       </c>
       <c r="K2" t="n">
-        <v>2.855</v>
+        <v>1.5412</v>
       </c>
       <c r="L2" t="n">
-        <v>0.1659</v>
+        <v>0.1244</v>
       </c>
       <c r="M2" t="n">
-        <v>0.0422</v>
+        <v>-1.1711</v>
       </c>
       <c r="N2" t="n">
-        <v>-0.058</v>
+        <v>-0.9255</v>
       </c>
       <c r="O2" t="n">
-        <v>0.1002</v>
+        <v>-0.2456</v>
       </c>
       <c r="P2" t="n">
-        <v>-1.6676</v>
+        <v>-0.7411</v>
       </c>
       <c r="Q2" t="n">
-        <v>-2.7793</v>
+        <v>-1.8529</v>
       </c>
       <c r="R2" t="n">
         <v>1.1117</v>
       </c>
       <c r="S2" t="n">
-        <v>4.567</v>
+        <v>1.1823</v>
       </c>
       <c r="T2" t="n">
-        <v>2.9323</v>
+        <v>1.9347</v>
       </c>
       <c r="U2" t="n">
-        <v>1.6347</v>
+        <v>-0.7524</v>
       </c>
       <c r="V2" t="n">
-        <v>0.6294</v>
+        <v>3.4616</v>
       </c>
       <c r="W2" t="n">
-        <v>1.2589</v>
+        <v>3.4616</v>
       </c>
       <c r="X2" t="n">
-        <v>-0.6294</v>
+        <v>0</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>D. MOUHAMED KHALIFA</t>
+          <t>M. GEDEAO YIMBU</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -643,73 +643,73 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>4.4448</v>
+        <v>3.6835</v>
       </c>
       <c r="E3" t="n">
-        <v>5.5028</v>
+        <v>2.6815</v>
       </c>
       <c r="F3" t="n">
-        <v>-1.058</v>
+        <v>1.002</v>
       </c>
       <c r="G3" t="n">
-        <v>0.4945</v>
+        <v>3.0631</v>
       </c>
       <c r="H3" t="n">
-        <v>0.6157</v>
+        <v>2.797</v>
       </c>
       <c r="I3" t="n">
-        <v>-0.1211</v>
+        <v>0.2661</v>
       </c>
       <c r="J3" t="n">
-        <v>1.6657</v>
+        <v>3.0209</v>
       </c>
       <c r="K3" t="n">
-        <v>1.5412</v>
+        <v>2.855</v>
       </c>
       <c r="L3" t="n">
-        <v>0.1244</v>
+        <v>0.1659</v>
       </c>
       <c r="M3" t="n">
-        <v>-1.1711</v>
+        <v>0.0422</v>
       </c>
       <c r="N3" t="n">
-        <v>-0.9255</v>
+        <v>-0.058</v>
       </c>
       <c r="O3" t="n">
-        <v>-0.2456</v>
+        <v>0.1002</v>
       </c>
       <c r="P3" t="n">
-        <v>-0.7411</v>
+        <v>-1.6676</v>
       </c>
       <c r="Q3" t="n">
-        <v>-1.8529</v>
+        <v>-2.7793</v>
       </c>
       <c r="R3" t="n">
         <v>1.1117</v>
       </c>
       <c r="S3" t="n">
-        <v>1.2299</v>
+        <v>1.6585</v>
       </c>
       <c r="T3" t="n">
-        <v>2.2284</v>
+        <v>1.1811</v>
       </c>
       <c r="U3" t="n">
-        <v>-0.9986</v>
+        <v>0.4775</v>
       </c>
       <c r="V3" t="n">
-        <v>3.4616</v>
+        <v>0.6294</v>
       </c>
       <c r="W3" t="n">
-        <v>3.4616</v>
+        <v>1.2589</v>
       </c>
       <c r="X3" t="n">
-        <v>0</v>
+        <v>-0.6294</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>J. PINILLA NUÑEZ</t>
+          <t>J. RIBEIROS CARREIRAS</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -721,73 +721,73 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>1.8662</v>
+        <v>2.3163</v>
       </c>
       <c r="E4" t="n">
-        <v>1.8662</v>
+        <v>2.0307</v>
       </c>
       <c r="F4" t="n">
-        <v>0</v>
+        <v>0.2857</v>
       </c>
       <c r="G4" t="n">
-        <v>1.8662</v>
+        <v>0.3713</v>
       </c>
       <c r="H4" t="n">
-        <v>0</v>
+        <v>1.445</v>
       </c>
       <c r="I4" t="n">
-        <v>1.8662</v>
+        <v>-1.0737</v>
       </c>
       <c r="J4" t="n">
-        <v>1.8662</v>
+        <v>-0.0162</v>
       </c>
       <c r="K4" t="n">
-        <v>0</v>
+        <v>1.2883</v>
       </c>
       <c r="L4" t="n">
-        <v>1.8662</v>
+        <v>-1.3045</v>
       </c>
       <c r="M4" t="n">
-        <v>0</v>
+        <v>0.3875</v>
       </c>
       <c r="N4" t="n">
-        <v>0</v>
+        <v>0.1567</v>
       </c>
       <c r="O4" t="n">
-        <v>0</v>
+        <v>0.2307</v>
       </c>
       <c r="P4" t="n">
-        <v>0</v>
+        <v>0.9264</v>
       </c>
       <c r="Q4" t="n">
         <v>0</v>
       </c>
       <c r="R4" t="n">
-        <v>0</v>
+        <v>0.9264</v>
       </c>
       <c r="S4" t="n">
-        <v>0</v>
+        <v>-0.5553</v>
       </c>
       <c r="T4" t="n">
-        <v>0</v>
+        <v>0.1586</v>
       </c>
       <c r="U4" t="n">
-        <v>0</v>
+        <v>-0.7138</v>
       </c>
       <c r="V4" t="n">
-        <v>0</v>
+        <v>1.5738</v>
       </c>
       <c r="W4" t="n">
-        <v>0</v>
+        <v>1.8883</v>
       </c>
       <c r="X4" t="n">
-        <v>0</v>
+        <v>-0.3144</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>D. VIGARIO CONSTANTINO</t>
+          <t>J. PINILLA NUÑEZ</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -799,37 +799,37 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>1.1511</v>
+        <v>1.8662</v>
       </c>
       <c r="E5" t="n">
-        <v>0.9877</v>
+        <v>1.8662</v>
       </c>
       <c r="F5" t="n">
-        <v>0.1634</v>
+        <v>0</v>
       </c>
       <c r="G5" t="n">
-        <v>1.1183</v>
+        <v>1.8662</v>
       </c>
       <c r="H5" t="n">
-        <v>1.1183</v>
+        <v>0</v>
       </c>
       <c r="I5" t="n">
-        <v>0</v>
+        <v>1.8662</v>
       </c>
       <c r="J5" t="n">
-        <v>0.9877</v>
+        <v>1.8662</v>
       </c>
       <c r="K5" t="n">
-        <v>0.9877</v>
+        <v>0</v>
       </c>
       <c r="L5" t="n">
-        <v>0</v>
+        <v>1.8662</v>
       </c>
       <c r="M5" t="n">
-        <v>0.1306</v>
+        <v>0</v>
       </c>
       <c r="N5" t="n">
-        <v>0.1306</v>
+        <v>0</v>
       </c>
       <c r="O5" t="n">
         <v>0</v>
@@ -844,13 +844,13 @@
         <v>0</v>
       </c>
       <c r="S5" t="n">
-        <v>0.0328</v>
+        <v>0</v>
       </c>
       <c r="T5" t="n">
         <v>0</v>
       </c>
       <c r="U5" t="n">
-        <v>0.0328</v>
+        <v>0</v>
       </c>
       <c r="V5" t="n">
         <v>0</v>
@@ -865,7 +865,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>J. RIBEIROS CARREIRAS</t>
+          <t>D. VIGARIO CONSTANTINO</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -877,67 +877,67 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>0.8637</v>
+        <v>1.2003</v>
       </c>
       <c r="E6" t="n">
-        <v>0.9966</v>
+        <v>0.9877</v>
       </c>
       <c r="F6" t="n">
-        <v>-0.1329</v>
+        <v>0.2126</v>
       </c>
       <c r="G6" t="n">
-        <v>0.3713</v>
+        <v>1.1183</v>
       </c>
       <c r="H6" t="n">
-        <v>1.445</v>
+        <v>1.1183</v>
       </c>
       <c r="I6" t="n">
-        <v>-1.0737</v>
+        <v>0</v>
       </c>
       <c r="J6" t="n">
-        <v>-0.0162</v>
+        <v>0.9877</v>
       </c>
       <c r="K6" t="n">
-        <v>1.2883</v>
+        <v>0.9877</v>
       </c>
       <c r="L6" t="n">
-        <v>-1.3045</v>
+        <v>0</v>
       </c>
       <c r="M6" t="n">
-        <v>0.3875</v>
+        <v>0.1306</v>
       </c>
       <c r="N6" t="n">
-        <v>0.1567</v>
+        <v>0.1306</v>
       </c>
       <c r="O6" t="n">
-        <v>0.2307</v>
+        <v>0</v>
       </c>
       <c r="P6" t="n">
-        <v>0.9264</v>
+        <v>0</v>
       </c>
       <c r="Q6" t="n">
         <v>0</v>
       </c>
       <c r="R6" t="n">
-        <v>0.9264</v>
+        <v>0</v>
       </c>
       <c r="S6" t="n">
-        <v>-2.0078</v>
+        <v>0.08210000000000001</v>
       </c>
       <c r="T6" t="n">
-        <v>-0.8754</v>
+        <v>0</v>
       </c>
       <c r="U6" t="n">
-        <v>-1.1324</v>
+        <v>0.08210000000000001</v>
       </c>
       <c r="V6" t="n">
-        <v>1.5738</v>
+        <v>0</v>
       </c>
       <c r="W6" t="n">
-        <v>1.8883</v>
+        <v>0</v>
       </c>
       <c r="X6" t="n">
-        <v>-0.3144</v>
+        <v>0</v>
       </c>
     </row>
     <row r="7">
@@ -955,13 +955,13 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>0.7186</v>
+        <v>1.0425</v>
       </c>
       <c r="E7" t="n">
-        <v>0.4275</v>
+        <v>0.776</v>
       </c>
       <c r="F7" t="n">
-        <v>0.2912</v>
+        <v>0.2665</v>
       </c>
       <c r="G7" t="n">
         <v>0.5373</v>
@@ -1000,13 +1000,13 @@
         <v>0.3706</v>
       </c>
       <c r="S7" t="n">
-        <v>-0.1893</v>
+        <v>0.1346</v>
       </c>
       <c r="T7" t="n">
-        <v>-0.0547</v>
+        <v>0.2938</v>
       </c>
       <c r="U7" t="n">
-        <v>-0.1346</v>
+        <v>-0.1592</v>
       </c>
       <c r="V7" t="n">
         <v>0</v>
@@ -1021,7 +1021,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>E. ANDRADE</t>
+          <t>J. PINILLA NUNEZ</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1033,73 +1033,73 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>0.1402</v>
+        <v>0.5488</v>
       </c>
       <c r="E8" t="n">
-        <v>1.751</v>
+        <v>2.1906</v>
       </c>
       <c r="F8" t="n">
-        <v>-1.6108</v>
+        <v>-1.6417</v>
       </c>
       <c r="G8" t="n">
-        <v>-0.9658</v>
+        <v>1.2919</v>
       </c>
       <c r="H8" t="n">
-        <v>-0.3668</v>
+        <v>1.496</v>
       </c>
       <c r="I8" t="n">
-        <v>-0.5991</v>
+        <v>-0.2041</v>
       </c>
       <c r="J8" t="n">
-        <v>-0.3841</v>
+        <v>3.4369</v>
       </c>
       <c r="K8" t="n">
-        <v>-0.4683</v>
+        <v>2.6276</v>
       </c>
       <c r="L8" t="n">
-        <v>0.0842</v>
+        <v>0.8093</v>
       </c>
       <c r="M8" t="n">
-        <v>-0.5817</v>
+        <v>-2.1449</v>
       </c>
       <c r="N8" t="n">
-        <v>0.1016</v>
+        <v>-1.1315</v>
       </c>
       <c r="O8" t="n">
-        <v>-0.6833</v>
+        <v>-1.0134</v>
       </c>
       <c r="P8" t="n">
-        <v>-0.3706</v>
+        <v>-1.8529</v>
       </c>
       <c r="Q8" t="n">
-        <v>-1.8529</v>
+        <v>-3.7057</v>
       </c>
       <c r="R8" t="n">
-        <v>1.4823</v>
+        <v>1.8529</v>
       </c>
       <c r="S8" t="n">
-        <v>0.2166</v>
+        <v>1.1114</v>
       </c>
       <c r="T8" t="n">
-        <v>0.2114</v>
+        <v>1.2022</v>
       </c>
       <c r="U8" t="n">
-        <v>0.0052</v>
+        <v>-0.09080000000000001</v>
       </c>
       <c r="V8" t="n">
-        <v>1.26</v>
+        <v>-0.0016</v>
       </c>
       <c r="W8" t="n">
-        <v>3.7766</v>
+        <v>1.2572</v>
       </c>
       <c r="X8" t="n">
-        <v>-2.5166</v>
+        <v>-1.2589</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>J. PINILLA NUNEZ</t>
+          <t>E. ANDRADE</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1111,67 +1111,67 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-0.1711</v>
+        <v>0.2994</v>
       </c>
       <c r="E9" t="n">
-        <v>1.1998</v>
+        <v>1.7625</v>
       </c>
       <c r="F9" t="n">
-        <v>-1.3709</v>
+        <v>-1.4631</v>
       </c>
       <c r="G9" t="n">
-        <v>1.2919</v>
+        <v>-0.9658</v>
       </c>
       <c r="H9" t="n">
-        <v>1.496</v>
+        <v>-0.3668</v>
       </c>
       <c r="I9" t="n">
-        <v>-0.2041</v>
+        <v>-0.5991</v>
       </c>
       <c r="J9" t="n">
-        <v>3.4369</v>
+        <v>-0.3841</v>
       </c>
       <c r="K9" t="n">
-        <v>2.6276</v>
+        <v>-0.4683</v>
       </c>
       <c r="L9" t="n">
-        <v>0.8093</v>
+        <v>0.0842</v>
       </c>
       <c r="M9" t="n">
-        <v>-2.1449</v>
+        <v>-0.5817</v>
       </c>
       <c r="N9" t="n">
-        <v>-1.1315</v>
+        <v>0.1016</v>
       </c>
       <c r="O9" t="n">
-        <v>-1.0134</v>
+        <v>-0.6833</v>
       </c>
       <c r="P9" t="n">
+        <v>-0.3706</v>
+      </c>
+      <c r="Q9" t="n">
         <v>-1.8529</v>
       </c>
-      <c r="Q9" t="n">
-        <v>-3.7057</v>
-      </c>
       <c r="R9" t="n">
-        <v>1.8529</v>
+        <v>1.4823</v>
       </c>
       <c r="S9" t="n">
-        <v>0.3914</v>
+        <v>0.3759</v>
       </c>
       <c r="T9" t="n">
-        <v>0.2114</v>
+        <v>0.2229</v>
       </c>
       <c r="U9" t="n">
-        <v>0.18</v>
+        <v>0.1529</v>
       </c>
       <c r="V9" t="n">
-        <v>-0.0016</v>
+        <v>1.26</v>
       </c>
       <c r="W9" t="n">
-        <v>1.2572</v>
+        <v>3.7766</v>
       </c>
       <c r="X9" t="n">
-        <v>-1.2589</v>
+        <v>-2.5166</v>
       </c>
     </row>
     <row r="10">
@@ -1189,13 +1189,13 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-0.8587</v>
+        <v>-1.1033</v>
       </c>
       <c r="E10" t="n">
-        <v>-1.0594</v>
+        <v>-1.3532</v>
       </c>
       <c r="F10" t="n">
-        <v>0.2007</v>
+        <v>0.2499</v>
       </c>
       <c r="G10" t="n">
         <v>0.2399</v>
@@ -1234,13 +1234,13 @@
         <v>0.1853</v>
       </c>
       <c r="S10" t="n">
-        <v>-0.043</v>
+        <v>-0.2876</v>
       </c>
       <c r="T10" t="n">
-        <v>0.434</v>
+        <v>0.1402</v>
       </c>
       <c r="U10" t="n">
-        <v>-0.477</v>
+        <v>-0.4278</v>
       </c>
       <c r="V10" t="n">
         <v>-0.3144</v>
@@ -1267,13 +1267,13 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-2.6384</v>
+        <v>-2.7237</v>
       </c>
       <c r="E11" t="n">
-        <v>1.6486</v>
+        <v>1.3664</v>
       </c>
       <c r="F11" t="n">
-        <v>-4.2871</v>
+        <v>-4.0901</v>
       </c>
       <c r="G11" t="n">
         <v>-0.144</v>
@@ -1312,13 +1312,13 @@
         <v>0.9264</v>
       </c>
       <c r="S11" t="n">
-        <v>0.3377</v>
+        <v>0.2524</v>
       </c>
       <c r="T11" t="n">
-        <v>1.3567</v>
+        <v>1.0744</v>
       </c>
       <c r="U11" t="n">
-        <v>-1.019</v>
+        <v>-0.822</v>
       </c>
       <c r="V11" t="n">
         <v>-2.8321</v>
@@ -1345,13 +1345,13 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>-3.5783</v>
+        <v>-2.7932</v>
       </c>
       <c r="E12" t="n">
-        <v>-0.7113</v>
+        <v>-0.2217</v>
       </c>
       <c r="F12" t="n">
-        <v>-2.867</v>
+        <v>-2.5715</v>
       </c>
       <c r="G12" t="n">
         <v>-1.8787</v>
@@ -1390,13 +1390,13 @@
         <v>1.4823</v>
       </c>
       <c r="S12" t="n">
-        <v>0.2268</v>
+        <v>1.0119</v>
       </c>
       <c r="T12" t="n">
-        <v>0.5397</v>
+        <v>1.0294</v>
       </c>
       <c r="U12" t="n">
-        <v>-0.3129</v>
+        <v>-0.0174</v>
       </c>
       <c r="V12" t="n">
         <v>-0.6294</v>
@@ -1423,13 +1423,13 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>-4.136</v>
+        <v>-3.793</v>
       </c>
       <c r="E13" t="n">
-        <v>-2.6387</v>
+        <v>-2.3449</v>
       </c>
       <c r="F13" t="n">
-        <v>-1.4973</v>
+        <v>-1.4481</v>
       </c>
       <c r="G13" t="n">
         <v>-1.9711</v>
@@ -1468,13 +1468,13 @@
         <v>0.7411</v>
       </c>
       <c r="S13" t="n">
-        <v>0.2057</v>
+        <v>0.5487</v>
       </c>
       <c r="T13" t="n">
-        <v>0.434</v>
+        <v>0.7278</v>
       </c>
       <c r="U13" t="n">
-        <v>-0.2283</v>
+        <v>-0.1791</v>
       </c>
       <c r="V13" t="n">
         <v>-1.2589</v>
@@ -1501,10 +1501,10 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>4.393999999999999</v>
+        <v>4.9411</v>
       </c>
       <c r="E14" t="n">
-        <v>14.4035</v>
+        <v>14.9508</v>
       </c>
       <c r="F14" t="n">
         <v>-10.0095</v>
@@ -1522,10 +1522,10 @@
         <v>8.872000000000002</v>
       </c>
       <c r="K14" t="n">
-        <v>8.181899999999999</v>
+        <v>8.181899999999997</v>
       </c>
       <c r="L14" t="n">
-        <v>0.6897000000000002</v>
+        <v>0.6897</v>
       </c>
       <c r="M14" t="n">
         <v>-4.8488</v>
@@ -1537,7 +1537,7 @@
         <v>-1.8028</v>
       </c>
       <c r="P14" t="n">
-        <v>-6.485</v>
+        <v>-6.484999999999999</v>
       </c>
       <c r="Q14" t="n">
         <v>-16.6758</v>
@@ -1546,13 +1546,13 @@
         <v>10.1907</v>
       </c>
       <c r="S14" t="n">
-        <v>4.9678</v>
+        <v>5.5149</v>
       </c>
       <c r="T14" t="n">
-        <v>7.417800000000001</v>
+        <v>7.9651</v>
       </c>
       <c r="U14" t="n">
-        <v>-2.4501</v>
+        <v>-2.45</v>
       </c>
       <c r="V14" t="n">
         <v>1.8884</v>
@@ -1579,13 +1579,13 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>5.5587</v>
+        <v>5.6085</v>
       </c>
       <c r="E15" t="n">
-        <v>4.8565</v>
+        <v>4.7586</v>
       </c>
       <c r="F15" t="n">
-        <v>0.7022</v>
+        <v>0.85</v>
       </c>
       <c r="G15" t="n">
         <v>2.5618</v>
@@ -1624,13 +1624,13 @@
         <v>2.4087</v>
       </c>
       <c r="S15" t="n">
-        <v>-0.6887</v>
+        <v>-0.6389</v>
       </c>
       <c r="T15" t="n">
-        <v>0.3084</v>
+        <v>0.2105</v>
       </c>
       <c r="U15" t="n">
-        <v>-0.9971</v>
+        <v>-0.8494</v>
       </c>
       <c r="V15" t="n">
         <v>2.2033</v>
@@ -1645,7 +1645,7 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>A. MENDEZ CARRION</t>
+          <t>A. MEJIA BERIGUETE</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1657,73 +1657,73 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>2.629</v>
+        <v>2.9411</v>
       </c>
       <c r="E16" t="n">
-        <v>2.019</v>
+        <v>2.5913</v>
       </c>
       <c r="F16" t="n">
-        <v>0.61</v>
+        <v>0.3497</v>
       </c>
       <c r="G16" t="n">
-        <v>2.4112</v>
+        <v>1.1881</v>
       </c>
       <c r="H16" t="n">
-        <v>1.1839</v>
+        <v>1.0411</v>
       </c>
       <c r="I16" t="n">
-        <v>1.2273</v>
+        <v>0.147</v>
       </c>
       <c r="J16" t="n">
-        <v>2.3846</v>
+        <v>1.6052</v>
       </c>
       <c r="K16" t="n">
-        <v>1.503</v>
+        <v>2.1726</v>
       </c>
       <c r="L16" t="n">
-        <v>0.8816000000000001</v>
+        <v>-0.5674</v>
       </c>
       <c r="M16" t="n">
-        <v>0.0266</v>
+        <v>-0.4171</v>
       </c>
       <c r="N16" t="n">
-        <v>-0.3191</v>
+        <v>-1.1315</v>
       </c>
       <c r="O16" t="n">
-        <v>0.3457</v>
+        <v>0.7144</v>
       </c>
       <c r="P16" t="n">
-        <v>1.297</v>
+        <v>1.8529</v>
       </c>
       <c r="Q16" t="n">
         <v>-0.9264</v>
       </c>
       <c r="R16" t="n">
-        <v>2.2234</v>
+        <v>2.7793</v>
       </c>
       <c r="S16" t="n">
-        <v>-0.1353</v>
+        <v>-0.7292999999999999</v>
       </c>
       <c r="T16" t="n">
-        <v>0.5609</v>
+        <v>0.0243</v>
       </c>
       <c r="U16" t="n">
-        <v>-0.6962</v>
+        <v>-0.7536</v>
       </c>
       <c r="V16" t="n">
-        <v>-0.9439</v>
+        <v>0.6294</v>
       </c>
       <c r="W16" t="n">
-        <v>0</v>
+        <v>1.8883</v>
       </c>
       <c r="X16" t="n">
-        <v>-0.9439</v>
+        <v>-1.2589</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>A. MEJIA BERIGUETE</t>
+          <t>A. MENDEZ CARRION</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1735,67 +1735,67 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>1.9842</v>
+        <v>1.9178</v>
       </c>
       <c r="E17" t="n">
-        <v>2.0038</v>
+        <v>1.5293</v>
       </c>
       <c r="F17" t="n">
-        <v>-0.0196</v>
+        <v>0.3884</v>
       </c>
       <c r="G17" t="n">
-        <v>1.1881</v>
+        <v>2.4112</v>
       </c>
       <c r="H17" t="n">
-        <v>1.0411</v>
+        <v>1.1839</v>
       </c>
       <c r="I17" t="n">
-        <v>0.147</v>
+        <v>1.2273</v>
       </c>
       <c r="J17" t="n">
-        <v>1.6052</v>
+        <v>2.3846</v>
       </c>
       <c r="K17" t="n">
-        <v>2.1726</v>
+        <v>1.503</v>
       </c>
       <c r="L17" t="n">
-        <v>-0.5674</v>
+        <v>0.8816000000000001</v>
       </c>
       <c r="M17" t="n">
-        <v>-0.4171</v>
+        <v>0.0266</v>
       </c>
       <c r="N17" t="n">
-        <v>-1.1315</v>
+        <v>-0.3191</v>
       </c>
       <c r="O17" t="n">
-        <v>0.7144</v>
+        <v>0.3457</v>
       </c>
       <c r="P17" t="n">
-        <v>1.8529</v>
+        <v>1.297</v>
       </c>
       <c r="Q17" t="n">
         <v>-0.9264</v>
       </c>
       <c r="R17" t="n">
-        <v>2.7793</v>
+        <v>2.2234</v>
       </c>
       <c r="S17" t="n">
-        <v>-1.6862</v>
+        <v>-0.8465</v>
       </c>
       <c r="T17" t="n">
-        <v>-0.5633</v>
+        <v>0.0712</v>
       </c>
       <c r="U17" t="n">
-        <v>-1.1229</v>
+        <v>-0.9177999999999999</v>
       </c>
       <c r="V17" t="n">
-        <v>0.6294</v>
+        <v>-0.9439</v>
       </c>
       <c r="W17" t="n">
-        <v>1.8883</v>
+        <v>0</v>
       </c>
       <c r="X17" t="n">
-        <v>-1.2589</v>
+        <v>-0.9439</v>
       </c>
     </row>
     <row r="18">
@@ -1891,13 +1891,13 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>0.6519</v>
+        <v>0.9211</v>
       </c>
       <c r="E19" t="n">
-        <v>3.181</v>
+        <v>3.4748</v>
       </c>
       <c r="F19" t="n">
-        <v>-2.5291</v>
+        <v>-2.5537</v>
       </c>
       <c r="G19" t="n">
         <v>-1.9974</v>
@@ -1936,13 +1936,13 @@
         <v>2.4087</v>
       </c>
       <c r="S19" t="n">
-        <v>-1.3681</v>
+        <v>-1.099</v>
       </c>
       <c r="T19" t="n">
-        <v>-0.0497</v>
+        <v>0.2441</v>
       </c>
       <c r="U19" t="n">
-        <v>-1.3184</v>
+        <v>-1.343</v>
       </c>
       <c r="V19" t="n">
         <v>3.4616</v>
@@ -2047,13 +2047,13 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-0.9379</v>
+        <v>-0.7426</v>
       </c>
       <c r="E21" t="n">
-        <v>-0.6562</v>
+        <v>-0.3624</v>
       </c>
       <c r="F21" t="n">
-        <v>-0.2818</v>
+        <v>-0.3802</v>
       </c>
       <c r="G21" t="n">
         <v>0.789</v>
@@ -2092,13 +2092,13 @@
         <v>1.8529</v>
       </c>
       <c r="S21" t="n">
-        <v>0.1619</v>
+        <v>0.3572</v>
       </c>
       <c r="T21" t="n">
-        <v>0.0809</v>
+        <v>0.3746</v>
       </c>
       <c r="U21" t="n">
-        <v>0.08110000000000001</v>
+        <v>-0.0174</v>
       </c>
       <c r="V21" t="n">
         <v>-1.8888</v>
@@ -2125,13 +2125,13 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-1.3046</v>
+        <v>-1.0103</v>
       </c>
       <c r="E22" t="n">
-        <v>0.9534</v>
+        <v>1.1492</v>
       </c>
       <c r="F22" t="n">
-        <v>-2.258</v>
+        <v>-2.1595</v>
       </c>
       <c r="G22" t="n">
         <v>-0.4673</v>
@@ -2170,13 +2170,13 @@
         <v>0.3706</v>
       </c>
       <c r="S22" t="n">
-        <v>-0.5785</v>
+        <v>-0.2841</v>
       </c>
       <c r="T22" t="n">
-        <v>0.2027</v>
+        <v>0.3986</v>
       </c>
       <c r="U22" t="n">
-        <v>-0.7812</v>
+        <v>-0.6827</v>
       </c>
       <c r="V22" t="n">
         <v>-0.6294</v>
@@ -2203,13 +2203,13 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>-2.5209</v>
+        <v>-2.5712</v>
       </c>
       <c r="E23" t="n">
-        <v>-0.8096</v>
+        <v>-0.6137</v>
       </c>
       <c r="F23" t="n">
-        <v>-1.7113</v>
+        <v>-1.9575</v>
       </c>
       <c r="G23" t="n">
         <v>-1.462</v>
@@ -2248,13 +2248,13 @@
         <v>0.5558999999999999</v>
       </c>
       <c r="S23" t="n">
-        <v>0.2736</v>
+        <v>0.2232</v>
       </c>
       <c r="T23" t="n">
-        <v>-0.2524</v>
+        <v>-0.0566</v>
       </c>
       <c r="U23" t="n">
-        <v>0.526</v>
+        <v>0.2798</v>
       </c>
       <c r="V23" t="n">
         <v>-1.8883</v>
@@ -2281,13 +2281,13 @@
         <v>1</v>
       </c>
       <c r="D24" t="n">
-        <v>-3.302</v>
+        <v>-3.4487</v>
       </c>
       <c r="E24" t="n">
-        <v>-2.7787</v>
+        <v>-2.9746</v>
       </c>
       <c r="F24" t="n">
-        <v>-0.5233</v>
+        <v>-0.4741</v>
       </c>
       <c r="G24" t="n">
         <v>0.0016</v>
@@ -2326,13 +2326,13 @@
         <v>0.9264</v>
       </c>
       <c r="S24" t="n">
-        <v>-0.4895</v>
+        <v>-0.6361</v>
       </c>
       <c r="T24" t="n">
-        <v>0.051</v>
+        <v>-0.1449</v>
       </c>
       <c r="U24" t="n">
-        <v>-0.5405</v>
+        <v>-0.4912</v>
       </c>
       <c r="V24" t="n">
         <v>-1.8877</v>
@@ -2359,13 +2359,13 @@
         <v>1</v>
       </c>
       <c r="D25" t="n">
-        <v>-4.2415</v>
+        <v>-4.1441</v>
       </c>
       <c r="E25" t="n">
-        <v>-3.2228</v>
+        <v>-3.0269</v>
       </c>
       <c r="F25" t="n">
-        <v>-1.0188</v>
+        <v>-1.1172</v>
       </c>
       <c r="G25" t="n">
         <v>-5.5046</v>
@@ -2404,13 +2404,13 @@
         <v>1.4823</v>
       </c>
       <c r="S25" t="n">
-        <v>-1.1985</v>
+        <v>-1.1012</v>
       </c>
       <c r="T25" t="n">
-        <v>0.09329999999999999</v>
+        <v>0.2891</v>
       </c>
       <c r="U25" t="n">
-        <v>-1.2918</v>
+        <v>-1.3903</v>
       </c>
       <c r="V25" t="n">
         <v>2.8321</v>
@@ -2437,13 +2437,13 @@
         <v>1</v>
       </c>
       <c r="D26" t="n">
-        <v>-4.7992</v>
+        <v>-5.7538</v>
       </c>
       <c r="E26" t="n">
-        <v>2.5748</v>
+        <v>1.5955</v>
       </c>
       <c r="F26" t="n">
-        <v>-7.374</v>
+        <v>-7.3493</v>
       </c>
       <c r="G26" t="n">
         <v>-3.4316</v>
@@ -2482,13 +2482,13 @@
         <v>1.6676</v>
       </c>
       <c r="S26" t="n">
-        <v>0.7413999999999999</v>
+        <v>-0.2133</v>
       </c>
       <c r="T26" t="n">
-        <v>2.0183</v>
+        <v>1.039</v>
       </c>
       <c r="U26" t="n">
-        <v>-1.2769</v>
+        <v>-1.2523</v>
       </c>
       <c r="V26" t="n">
         <v>-3.7766</v>
@@ -2515,13 +2515,13 @@
         <v>1</v>
       </c>
       <c r="D27" t="n">
-        <v>-4.394000000000001</v>
+        <v>-4.3939</v>
       </c>
       <c r="E27" t="n">
-        <v>10.0095</v>
+        <v>10.0094</v>
       </c>
       <c r="F27" t="n">
-        <v>-14.4037</v>
+        <v>-14.4034</v>
       </c>
       <c r="G27" t="n">
         <v>-4.0229</v>
@@ -2560,13 +2560,13 @@
         <v>16.6758</v>
       </c>
       <c r="S27" t="n">
-        <v>-4.9679</v>
+        <v>-4.968</v>
       </c>
       <c r="T27" t="n">
-        <v>2.4501</v>
+        <v>2.4499</v>
       </c>
       <c r="U27" t="n">
-        <v>-7.417899999999999</v>
+        <v>-7.4179</v>
       </c>
       <c r="V27" t="n">
         <v>-1.888300000000001</v>
